--- a/resultados/matriz_causa_manipulacion.xlsx
+++ b/resultados/matriz_causa_manipulacion.xlsx
@@ -436,37 +436,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>DESGASTE_NORMAL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MAL_USO_CONFIGURACION</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MAL_ALMACENAMIENTO_TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MALA_LIMPIEZA_MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MAL_MANEJO_CABLES</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>FALTA_CAPACITACION</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAL_TRATO_FISICO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>MAL_ALMACENAMIENTO_TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MAL_USO_CONFIGURACION</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>MALA_LIMPIEZA_MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>DESGASTE_NORMAL</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>MAL_MANEJO_CABLES</t>
         </is>
       </c>
     </row>
@@ -477,25 +477,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="C2" t="n">
-        <v>723</v>
+        <v>484</v>
       </c>
       <c r="D2" t="n">
         <v>213</v>
       </c>
       <c r="E2" t="n">
-        <v>484</v>
+        <v>329</v>
       </c>
       <c r="F2" t="n">
-        <v>329</v>
+        <v>870</v>
       </c>
       <c r="G2" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>870</v>
+        <v>723</v>
       </c>
     </row>
     <row r="3">
@@ -505,25 +505,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="D3" t="n">
         <v>37</v>
       </c>
       <c r="E3" t="n">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>143</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -533,25 +533,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>263</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
         <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>169</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>80</v>
@@ -570,16 +570,16 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
+        <v>73</v>
+      </c>
+      <c r="F5" t="n">
+        <v>82</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>80</v>
-      </c>
-      <c r="F5" t="n">
-        <v>73</v>
-      </c>
-      <c r="G5" t="n">
-        <v>14</v>
-      </c>
-      <c r="H5" t="n">
-        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -589,25 +589,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -632,10 +632,10 @@
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -648,13 +648,13 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -682,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -704,13 +704,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -732,16 +732,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
